--- a/test_doc/new_org/syllabus_5_english.xlsx
+++ b/test_doc/new_org/syllabus_5_english.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grammar: Nouns and Articles</t>
+          <t>Writing: Paragraphs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Naming words</t>
+          <t>Structure of a paragraph</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -521,26 +521,26 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>A, an, the</t>
+          <t>Guided writing</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prose: Flying Together</t>
+          <t>Grammar: Verbs and Tenses</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reading and comprehension</t>
+          <t>Simple tenses</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,56 +551,56 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Story discussion</t>
+          <t>Subject-verb agreement</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Writing: Sentences</t>
+          <t>Grammar: Nouns and Pronouns</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Making sentences</t>
+          <t>Kinds of nouns</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Punctuation</t>
+          <t>Pronoun usage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grammar: Verbs and Tenses</t>
+          <t>Poetry: A House, A Home</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Action words</t>
+          <t>Recitation and meaning</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Past and present</t>
+          <t>Appreciation</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -621,7 +621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prose: The Talkative Barber</t>
+          <t>Prose: Flying Together</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -641,101 +641,11 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Retelling</t>
+          <t>Story discussion</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Writing: Short Paragraphs</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>My family</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>My school day</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Poetry: Class Discussion</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Recitation</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Grammar: Describing Words</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Adjectives</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Opposites</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
